--- a/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026_ELK_BULL_CWMU.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026_ELK_BULL_CWMU.xlsx
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N67"/>
+  <dimension ref="A1:O67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -535,6 +535,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -598,10 +599,15 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Average Harvest Age Prior Year</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
+          <t>Average Harvest Age</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Current Age (3-Yr Avg)</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>Avg Days Hunted Prior Year</t>
         </is>
@@ -669,7 +675,8 @@
         </is>
       </c>
       <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -737,7 +744,8 @@
         </is>
       </c>
       <c r="M5" s="6" t="inlineStr"/>
-      <c r="N5" s="6" t="inlineStr">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" s="6" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
@@ -805,7 +813,8 @@
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
@@ -873,7 +882,8 @@
         </is>
       </c>
       <c r="M7" s="6" t="inlineStr"/>
-      <c r="N7" s="6" t="inlineStr">
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" s="6" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
@@ -941,7 +951,8 @@
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr"/>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
@@ -1009,7 +1020,8 @@
         </is>
       </c>
       <c r="M9" s="6" t="inlineStr"/>
-      <c r="N9" s="6" t="inlineStr">
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" s="6" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
@@ -1077,7 +1089,8 @@
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr"/>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
@@ -1145,7 +1158,8 @@
         </is>
       </c>
       <c r="M11" s="6" t="inlineStr"/>
-      <c r="N11" s="6" t="inlineStr">
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -1213,7 +1227,8 @@
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr"/>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" s="4" t="inlineStr">
         <is>
           <t>2.9</t>
         </is>
@@ -1281,7 +1296,8 @@
         </is>
       </c>
       <c r="M13" s="6" t="inlineStr"/>
-      <c r="N13" s="6" t="inlineStr">
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1349,7 +1365,8 @@
         </is>
       </c>
       <c r="M14" s="4" t="inlineStr"/>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" s="4" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
@@ -1417,7 +1434,8 @@
         </is>
       </c>
       <c r="M15" s="6" t="inlineStr"/>
-      <c r="N15" s="6" t="inlineStr">
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1485,7 +1503,8 @@
         </is>
       </c>
       <c r="M16" s="4" t="inlineStr"/>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" s="4" t="inlineStr">
         <is>
           <t>3.8</t>
         </is>
@@ -1553,7 +1572,8 @@
         </is>
       </c>
       <c r="M17" s="6" t="inlineStr"/>
-      <c r="N17" s="6" t="inlineStr">
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" s="6" t="inlineStr">
         <is>
           <t>9.2</t>
         </is>
@@ -1621,7 +1641,8 @@
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr"/>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" s="4" t="inlineStr">
         <is>
           <t>3.6</t>
         </is>
@@ -1689,7 +1710,8 @@
         </is>
       </c>
       <c r="M19" s="6" t="inlineStr"/>
-      <c r="N19" s="6" t="inlineStr">
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" s="6" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
@@ -1757,7 +1779,8 @@
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr"/>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" s="4" t="inlineStr">
         <is>
           <t>3.8</t>
         </is>
@@ -1825,7 +1848,8 @@
         </is>
       </c>
       <c r="M21" s="6" t="inlineStr"/>
-      <c r="N21" s="6" t="inlineStr">
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" s="6" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
@@ -1893,7 +1917,8 @@
         </is>
       </c>
       <c r="M22" s="4" t="inlineStr"/>
-      <c r="N22" s="4" t="inlineStr">
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -1961,7 +1986,8 @@
         </is>
       </c>
       <c r="M23" s="6" t="inlineStr"/>
-      <c r="N23" s="6" t="inlineStr">
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" s="6" t="inlineStr">
         <is>
           <t>5.9</t>
         </is>
@@ -2029,7 +2055,8 @@
         </is>
       </c>
       <c r="M24" s="4" t="inlineStr"/>
-      <c r="N24" s="4" t="inlineStr">
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" s="4" t="inlineStr">
         <is>
           <t>1.9</t>
         </is>
@@ -2097,7 +2124,8 @@
         </is>
       </c>
       <c r="M25" s="6" t="inlineStr"/>
-      <c r="N25" s="6" t="inlineStr">
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" s="6" t="inlineStr">
         <is>
           <t>5.2</t>
         </is>
@@ -2165,7 +2193,8 @@
         </is>
       </c>
       <c r="M26" s="4" t="inlineStr"/>
-      <c r="N26" s="4" t="inlineStr">
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" s="4" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
@@ -2233,7 +2262,8 @@
         </is>
       </c>
       <c r="M27" s="6" t="inlineStr"/>
-      <c r="N27" s="6" t="inlineStr">
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" s="6" t="inlineStr">
         <is>
           <t>5.7</t>
         </is>
@@ -2301,7 +2331,8 @@
         </is>
       </c>
       <c r="M28" s="4" t="inlineStr"/>
-      <c r="N28" s="4" t="inlineStr">
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" s="4" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
@@ -2369,7 +2400,8 @@
         </is>
       </c>
       <c r="M29" s="6" t="inlineStr"/>
-      <c r="N29" s="6" t="inlineStr">
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -2437,7 +2469,8 @@
         </is>
       </c>
       <c r="M30" s="4" t="inlineStr"/>
-      <c r="N30" s="4" t="inlineStr">
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" s="4" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
@@ -2505,7 +2538,8 @@
         </is>
       </c>
       <c r="M31" s="6" t="inlineStr"/>
-      <c r="N31" s="6" t="inlineStr">
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2573,7 +2607,8 @@
         </is>
       </c>
       <c r="M32" s="4" t="inlineStr"/>
-      <c r="N32" s="4" t="inlineStr">
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" s="4" t="inlineStr">
         <is>
           <t>3.6</t>
         </is>
@@ -2641,7 +2676,8 @@
         </is>
       </c>
       <c r="M33" s="6" t="inlineStr"/>
-      <c r="N33" s="6" t="inlineStr">
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" s="6" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
@@ -2709,7 +2745,8 @@
         </is>
       </c>
       <c r="M34" s="4" t="inlineStr"/>
-      <c r="N34" s="4" t="inlineStr">
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" s="4" t="inlineStr">
         <is>
           <t>6.6</t>
         </is>
@@ -2777,7 +2814,8 @@
         </is>
       </c>
       <c r="M35" s="6" t="inlineStr"/>
-      <c r="N35" s="6" t="inlineStr">
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" s="6" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
@@ -2845,7 +2883,8 @@
         </is>
       </c>
       <c r="M36" s="4" t="inlineStr"/>
-      <c r="N36" s="4" t="inlineStr">
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" s="4" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
@@ -2913,7 +2952,8 @@
         </is>
       </c>
       <c r="M37" s="6" t="inlineStr"/>
-      <c r="N37" s="6" t="inlineStr">
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" s="6" t="inlineStr">
         <is>
           <t>9.4</t>
         </is>
@@ -2981,7 +3021,8 @@
         </is>
       </c>
       <c r="M38" s="4" t="inlineStr"/>
-      <c r="N38" s="4" t="inlineStr">
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" s="4" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
@@ -3049,7 +3090,8 @@
         </is>
       </c>
       <c r="M39" s="6" t="inlineStr"/>
-      <c r="N39" s="6" t="inlineStr">
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" s="6" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
@@ -3117,7 +3159,8 @@
         </is>
       </c>
       <c r="M40" s="4" t="inlineStr"/>
-      <c r="N40" s="4" t="inlineStr">
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" s="4" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
@@ -3185,7 +3228,8 @@
         </is>
       </c>
       <c r="M41" s="6" t="inlineStr"/>
-      <c r="N41" s="6" t="inlineStr">
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" s="6" t="inlineStr">
         <is>
           <t>7.5</t>
         </is>
@@ -3253,7 +3297,8 @@
         </is>
       </c>
       <c r="M42" s="4" t="inlineStr"/>
-      <c r="N42" s="4" t="inlineStr">
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -3321,7 +3366,8 @@
         </is>
       </c>
       <c r="M43" s="6" t="inlineStr"/>
-      <c r="N43" s="6" t="inlineStr">
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" s="6" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
@@ -3389,7 +3435,8 @@
         </is>
       </c>
       <c r="M44" s="4" t="inlineStr"/>
-      <c r="N44" s="4" t="inlineStr">
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" s="4" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
@@ -3457,7 +3504,8 @@
         </is>
       </c>
       <c r="M45" s="6" t="inlineStr"/>
-      <c r="N45" s="6" t="inlineStr">
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" s="6" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -3525,7 +3573,8 @@
         </is>
       </c>
       <c r="M46" s="4" t="inlineStr"/>
-      <c r="N46" s="4" t="inlineStr">
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" s="4" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
@@ -3593,7 +3642,8 @@
         </is>
       </c>
       <c r="M47" s="6" t="inlineStr"/>
-      <c r="N47" s="6" t="inlineStr">
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -3661,7 +3711,8 @@
         </is>
       </c>
       <c r="M48" s="4" t="inlineStr"/>
-      <c r="N48" s="4" t="inlineStr">
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" s="4" t="inlineStr">
         <is>
           <t>6.8</t>
         </is>
@@ -3729,7 +3780,8 @@
         </is>
       </c>
       <c r="M49" s="6" t="inlineStr"/>
-      <c r="N49" s="6" t="inlineStr">
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" s="6" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
@@ -3797,7 +3849,8 @@
         </is>
       </c>
       <c r="M50" s="4" t="inlineStr"/>
-      <c r="N50" s="4" t="inlineStr">
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" s="4" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
@@ -3865,7 +3918,8 @@
         </is>
       </c>
       <c r="M51" s="6" t="inlineStr"/>
-      <c r="N51" s="6" t="inlineStr">
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" s="6" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
@@ -3933,7 +3987,8 @@
         </is>
       </c>
       <c r="M52" s="4" t="inlineStr"/>
-      <c r="N52" s="4" t="inlineStr">
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -4001,7 +4056,8 @@
         </is>
       </c>
       <c r="M53" s="6" t="inlineStr"/>
-      <c r="N53" s="6" t="inlineStr">
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" s="6" t="inlineStr">
         <is>
           <t>5.9</t>
         </is>
@@ -4069,7 +4125,8 @@
         </is>
       </c>
       <c r="M54" s="4" t="inlineStr"/>
-      <c r="N54" s="4" t="inlineStr">
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" s="4" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
@@ -4137,7 +4194,8 @@
         </is>
       </c>
       <c r="M55" s="6" t="inlineStr"/>
-      <c r="N55" s="6" t="inlineStr">
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -4205,7 +4263,8 @@
         </is>
       </c>
       <c r="M56" s="4" t="inlineStr"/>
-      <c r="N56" s="4" t="inlineStr">
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" s="4" t="inlineStr">
         <is>
           <t>3.8</t>
         </is>
@@ -4273,7 +4332,8 @@
         </is>
       </c>
       <c r="M57" s="6" t="inlineStr"/>
-      <c r="N57" s="6" t="inlineStr">
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" s="6" t="inlineStr">
         <is>
           <t>3.9</t>
         </is>
@@ -4341,7 +4401,8 @@
         </is>
       </c>
       <c r="M58" s="4" t="inlineStr"/>
-      <c r="N58" s="4" t="inlineStr">
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" s="4" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
@@ -4409,7 +4470,8 @@
         </is>
       </c>
       <c r="M59" s="6" t="inlineStr"/>
-      <c r="N59" s="6" t="inlineStr">
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" s="6" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
@@ -4477,7 +4539,8 @@
         </is>
       </c>
       <c r="M60" s="4" t="inlineStr"/>
-      <c r="N60" s="4" t="inlineStr">
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" s="4" t="inlineStr">
         <is>
           <t>7.5</t>
         </is>
@@ -4545,7 +4608,8 @@
         </is>
       </c>
       <c r="M61" s="6" t="inlineStr"/>
-      <c r="N61" s="6" t="inlineStr">
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -4613,7 +4677,8 @@
         </is>
       </c>
       <c r="M62" s="4" t="inlineStr"/>
-      <c r="N62" s="4" t="inlineStr">
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" s="4" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
@@ -4681,7 +4746,8 @@
         </is>
       </c>
       <c r="M63" s="6" t="inlineStr"/>
-      <c r="N63" s="6" t="inlineStr">
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" s="6" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
@@ -4749,7 +4815,8 @@
         </is>
       </c>
       <c r="M64" s="4" t="inlineStr"/>
-      <c r="N64" s="4" t="inlineStr">
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" s="4" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
@@ -4817,7 +4884,8 @@
         </is>
       </c>
       <c r="M65" s="6" t="inlineStr"/>
-      <c r="N65" s="6" t="inlineStr">
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" s="6" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
@@ -4885,7 +4953,8 @@
         </is>
       </c>
       <c r="M66" s="4" t="inlineStr"/>
-      <c r="N66" s="4" t="inlineStr">
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" s="4" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
@@ -4949,7 +5018,8 @@
       </c>
       <c r="L67" s="6" t="inlineStr"/>
       <c r="M67" s="6" t="inlineStr"/>
-      <c r="N67" s="6" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:N67"/>
